--- a/runs/RELX/2026-10-14/bear/scratch/g_beta_peer/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/g_beta_peer/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2127.919387139865</v>
+        <v>2174.74477669413</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.09208</v>
+        <v>0.08606720000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.08636291564</v>
+        <v>0.08112083634400001</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11375.27792768993</v>
+        <v>11510.40545083869</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>43386.75443215058</v>
+        <v>47107.85546305522</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>29886.14985201185</v>
+        <v>33163.41647340442</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>41261.42777970178</v>
+        <v>44673.82192424312</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>34264.42777970178</v>
+        <v>37676.82192424312</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>33439.65365765108</v>
+        <v>36921.62449466455</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>19.17681032766662</v>
+        <v>21.173634068471</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1917.681032766662</v>
+        <v>2117.3634068471</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.307946217</v>
+        <v>-0.2358847323</v>
       </c>
     </row>
   </sheetData>
